--- a/reports/TeacherRegisterReport.xlsx
+++ b/reports/TeacherRegisterReport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{18E1EBA3-3127-4CB2-8EBC-3D91F4BA1181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{FDE47CF4-DDEC-4BF7-81D1-BEE1DAFB17D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-384000" yWindow="-384000" windowWidth="2388" windowHeight="564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register Report" sheetId="1" r:id="rId1"/>
@@ -423,6 +423,7 @@
   <cols>
     <col min="1" max="1" width="31.44140625" customWidth="1"/>
     <col min="2" max="2" width="17.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="5" max="5" width="65.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
